--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/nov-2025.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/nov-2025.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M81"/>
+  <dimension ref="A1:M79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>46137490</v>
+        <v>49308.13</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>18081000.42</v>
+        <v>19323.55</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>37160999.89</v>
+        <v>39714.76</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>23902199.58</v>
+        <v>25544.79</v>
       </c>
     </row>
     <row r="6">
@@ -809,11 +809,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>23746212</v>
+        <v>25378.09</v>
       </c>
     </row>
     <row r="7">
@@ -870,11 +870,11 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>69258000</v>
+        <v>74017.50999999999</v>
       </c>
     </row>
     <row r="8">
@@ -935,11 +935,11 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>68694796.8</v>
+        <v>73415.60000000001</v>
       </c>
     </row>
     <row r="9">
@@ -996,11 +996,11 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>8802192</v>
+        <v>9407.09</v>
       </c>
     </row>
     <row r="10">
@@ -1057,11 +1057,11 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>23146886</v>
+        <v>24737.57</v>
       </c>
     </row>
     <row r="11">
@@ -1118,11 +1118,11 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>23337090</v>
+        <v>24940.85</v>
       </c>
     </row>
     <row r="12">
@@ -1179,11 +1179,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>67068400</v>
+        <v>71677.44</v>
       </c>
     </row>
     <row r="13">
@@ -1240,11 +1240,11 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>44034900.42</v>
+        <v>47061.04</v>
       </c>
     </row>
     <row r="14">
@@ -1301,11 +1301,11 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>22376760</v>
+        <v>23914.52</v>
       </c>
     </row>
     <row r="15">
@@ -1362,11 +1362,11 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>46674180</v>
+        <v>49881.7</v>
       </c>
     </row>
     <row r="16">
@@ -1423,11 +1423,11 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>17999999.5</v>
+        <v>19236.99</v>
       </c>
     </row>
     <row r="17">
@@ -1484,11 +1484,11 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>49964649</v>
+        <v>53398.29</v>
       </c>
     </row>
     <row r="18">
@@ -1545,11 +1545,11 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>35022652</v>
+        <v>37429.46</v>
       </c>
     </row>
     <row r="19">
@@ -1610,11 +1610,11 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>133022056.79</v>
+        <v>142163.53</v>
       </c>
     </row>
     <row r="20">
@@ -1675,11 +1675,11 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>134196300</v>
+        <v>143418.47</v>
       </c>
     </row>
     <row r="21">
@@ -1736,11 +1736,11 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>33546100</v>
+        <v>35851.44</v>
       </c>
     </row>
     <row r="22">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>226715421.59</v>
+        <v>242295.64</v>
       </c>
     </row>
     <row r="23">
@@ -1862,11 +1862,11 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>24454500</v>
+        <v>26135.05</v>
       </c>
     </row>
     <row r="24">
@@ -1923,11 +1923,11 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>50313200</v>
+        <v>53770.8</v>
       </c>
     </row>
     <row r="25">
@@ -1984,11 +1984,11 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>53819416</v>
+        <v>57517.96</v>
       </c>
     </row>
     <row r="26">
@@ -2045,11 +2045,11 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>56882000</v>
+        <v>60791.01</v>
       </c>
     </row>
     <row r="27">
@@ -2106,11 +2106,11 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>53819416</v>
+        <v>57517.96</v>
       </c>
     </row>
     <row r="28">
@@ -2167,11 +2167,11 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>69020000</v>
+        <v>73763.16</v>
       </c>
     </row>
     <row r="29">
@@ -2228,11 +2228,11 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>50322363</v>
+        <v>53780.59</v>
       </c>
     </row>
     <row r="30">
@@ -2289,11 +2289,11 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>26920061</v>
+        <v>28770.05</v>
       </c>
     </row>
     <row r="31">
@@ -2350,11 +2350,11 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>45600800</v>
+        <v>48734.55</v>
       </c>
     </row>
     <row r="32">
@@ -2411,11 +2411,11 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>26920061</v>
+        <v>28770.05</v>
       </c>
     </row>
     <row r="33">
@@ -2476,11 +2476,11 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>196706702.5</v>
+        <v>210224.67</v>
       </c>
     </row>
     <row r="34">
@@ -2541,11 +2541,11 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>223125000</v>
+        <v>238458.48</v>
       </c>
     </row>
     <row r="35">
@@ -2602,11 +2602,11 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>23337090</v>
+        <v>24940.85</v>
       </c>
     </row>
     <row r="36">
@@ -2663,11 +2663,11 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>69514183.2</v>
+        <v>74291.3</v>
       </c>
     </row>
     <row r="37">
@@ -2724,11 +2724,11 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>20321998.9</v>
+        <v>21718.56</v>
       </c>
     </row>
     <row r="38">
@@ -2785,11 +2785,11 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>33570799.64</v>
+        <v>35877.83</v>
       </c>
     </row>
     <row r="39">
@@ -2846,11 +2846,11 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>26909708</v>
+        <v>28758.98</v>
       </c>
     </row>
     <row r="40">
@@ -2907,17 +2907,17 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>31203899.16</v>
+        <v>33348.28</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2412-1059-CM25</t>
+          <t>425-843-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2937,17 +2937,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.254.100-6</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LO PRADO</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2957,28 +2957,28 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>9623292</v>
+        <v>23952.6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>425-843-CM25</t>
+          <t>4229-171-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2998,48 +2998,48 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.954.400-5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>Carabineros de Chile - VIII Zona Bio Bio</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>22412383.84</v>
+        <v>53807.51</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>4229-171-CM25</t>
+          <t>2412-1059-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3064,37 +3064,37 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.954.400-5</t>
+          <t>69.254.100-6</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - VIII Zona Bio Bio</t>
+          <t>I MUNICIPALIDAD DE LO PRADO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>86.385.500-4</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>50347551.73</v>
+        <v>10284.62</v>
       </c>
     </row>
     <row r="44">
@@ -3151,11 +3151,11 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>26909708</v>
+        <v>28758.98</v>
       </c>
     </row>
     <row r="45">
@@ -3212,11 +3212,11 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>21150800.58</v>
+        <v>22604.31</v>
       </c>
     </row>
     <row r="46">
@@ -3273,11 +3273,11 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>23121700</v>
+        <v>24710.66</v>
       </c>
     </row>
     <row r="47">
@@ -3334,11 +3334,11 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>53704445.34</v>
+        <v>57395.09</v>
       </c>
     </row>
     <row r="48">
@@ -3395,17 +3395,17 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>16053100</v>
+        <v>17156.29</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>4230-175-CM25</t>
+          <t>587-795-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3420,53 +3420,53 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Solicitud de Cancelacion</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Valdivia</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>MEDITERRANEO AUTOMOTORES S A</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>96.889.440-4</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>23902199.58</v>
+        <v>25383.2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5482-144-CM25</t>
+          <t>4232-159-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3486,48 +3486,48 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.070.500-1</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NUNOA</t>
+          <t>Carabineros de Chile - Prefectura Arica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>62953380</v>
+        <v>29060.14</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1080164-35-CM25</t>
+          <t>1080164-33-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3578,17 +3578,17 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>23337090</v>
+        <v>29060.14</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>587-795-CM25</t>
+          <t>1080164-35-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3613,43 +3613,43 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.801.000-7</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>ESCUELA DE SUBOFICIALES GRUPO ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>23751000.56</v>
+        <v>24940.85</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>4232-159-CM25</t>
+          <t>5482-144-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3669,48 +3669,48 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>69.070.500-1</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>I MUNICIPALIDAD DE NUNOA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.005.909-9</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>27191500</v>
+        <v>67279.63</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1080164-33-CM25</t>
+          <t>784642-53-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3735,43 +3735,43 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>ESCUELA DE SUBOFICIALES GRUPO ANTOFAGASTA</t>
+          <t>Dirección de Educación, Doctrina e Historia de Car</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.005.909-9</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>27191500</v>
+        <v>25383.2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2974-633-CM25</t>
+          <t>634-1060-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3786,22 +3786,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Solicitud de Cancelacion</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.103.006-1</t>
+          <t>61.004.000-4</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3811,28 +3811,28 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>96.889.440-4</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>43000000.26</v>
+        <v>35766.48</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>784642-53-CM25</t>
+          <t>1147293-331-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3847,22 +3847,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>70.930.000-8</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Car</t>
+          <t>Fundación para la Innovación Agraria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3872,28 +3872,28 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>23751000.56</v>
+        <v>25276.22</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>634-1060-CM25</t>
+          <t>634-1055-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3944,17 +3944,17 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>33466608</v>
+        <v>71532.96000000001</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>634-1055-CM25</t>
+          <t>2546-995-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3974,48 +3974,48 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.004.000-4</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>MEDITERRANEO AUTOMOTORES S A</t>
+          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>96.889.440-4</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>66933216</v>
+        <v>25856.53</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1147293-331-CM25</t>
+          <t>1340-9067-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4040,43 +4040,43 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>70.930.000-8</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fundación para la Innovación Agraria</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>Automotriz Tecnosur Limitada</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>78.585.230-3</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>23650900.14</v>
+        <v>24023.9</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1340-9067-CM25</t>
+          <t>3326-545-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4096,48 +4096,52 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Automotriz Tecnosur Limitada</t>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>78.585.230-3</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
+          <t>96.928.530-4</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>22479100</v>
+        <v>77787.06</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3326-545-CM25</t>
+          <t>2767-124-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4152,22 +4156,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>69.072.000-0</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4185,24 +4189,20 @@
           <t>96.928.530-4</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>72785155.23999999</v>
+        <v>19446.76</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2546-995-CM25</t>
+          <t>3853-803-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4227,43 +4227,43 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>69.201.000-0</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>I MUNICIPALIDAD DE RIO BUENO</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.005.909-9</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>24193890</v>
+        <v>73273.67999999999</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2767-124-CM25</t>
+          <t>5890-187-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4283,17 +4283,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>69.072.000-0</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CISTERNA</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4303,28 +4303,28 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>96.928.530-4</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>18196288.81</v>
+        <v>41718.08</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3853-803-CM25</t>
+          <t>4020-1383-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4349,43 +4349,43 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>69.201.000-0</t>
+          <t>69.160.500-0</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO BUENO</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>68561999.94</v>
+        <v>31111.44</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>5890-187-CM25</t>
+          <t>2271-230-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4405,17 +4405,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4425,28 +4425,28 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>96.928.530-4</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>39035499.79</v>
+        <v>41182.73</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>4020-1383-CM25</t>
+          <t>2981-1601-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4466,48 +4466,48 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>69.160.500-0</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANETE</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>29110899.79</v>
+        <v>41718.08</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2271-230-CM25</t>
+          <t>1447930-322-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4527,17 +4527,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>61.999.390-K</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>SUBSECRETARIA DE SEGURIDAD PUBLICA</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4547,28 +4547,28 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>96.928.530-4</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>38534580</v>
+        <v>41640.32</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2981-1601-CM25</t>
+          <t>2129-336-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4583,53 +4583,53 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>69.150.300-3</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>Ilustre Municipalidad de Ranquil</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>39035499.79</v>
+        <v>20704.55</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1447930-322-CM25</t>
+          <t>3326-597-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.999.390-K</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SEGURIDAD PUBLICA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4669,28 +4669,28 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>38962742</v>
+        <v>49881.7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2129-336-CM25</t>
+          <t>727202-3302-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4715,43 +4715,43 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>69.150.300-3</t>
+          <t>69.040.500-8</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Ranquil</t>
+          <t>I MUNICIPALIDAD DE VICUNA</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>76.141.853-k</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>19373200</v>
+        <v>29061.41</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3326-597-CM25</t>
+          <t>29-589-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.103.035-5</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4791,28 +4791,28 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>46674180</v>
+        <v>48739.81</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>727202-3302-CM25</t>
+          <t>552578-137-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4837,43 +4837,43 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>69.040.500-8</t>
+          <t>69.264.500-6</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICUNA</t>
+          <t>I MUNICIPALIDAD DE SAN RAFAEL</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>27192690</v>
+        <v>28758.98</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>29-589-CM25</t>
+          <t>4090-386-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4898,43 +4898,43 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.103.035-5</t>
+          <t>69.220.500-6</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>I MUNICIPALIDAD DE MAULLIN</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>45605714</v>
+        <v>39714.76</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>552578-137-CM25</t>
+          <t>1347776-13-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4954,48 +4954,48 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>69.264.500-6</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN RAFAEL</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>DIFOR CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>96.918.300-5</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>26909708</v>
+        <v>60791.01</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>796305-80-CM25</t>
+          <t>2673-227-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5020,43 +5020,43 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.103.006-1</t>
+          <t>69.072.900-8</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>76.141.853-k</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>16411052</v>
+        <v>43687.79</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1347776-13-CM25</t>
+          <t>995118-180-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.954.400-5</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>VIII Zona de Carabineros Bio Bío</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5096,28 +5096,28 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>DIFOR CHILE SOCIEDAD ANONIMA</t>
+          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>96.918.300-5</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>56882000</v>
+        <v>49881.7</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2673-227-CM25</t>
+          <t>796305-80-CM25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5142,43 +5142,43 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>69.072.900-8</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
+          <t>Division de Bienestar Social</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>40878558.7</v>
+        <v>17538.84</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>995118-180-CM25</t>
+          <t>2974-641-CM25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5203,43 +5203,43 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.954.400-5</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>VIII Zona de Carabineros Bio Bío</t>
+          <t>Division de Bienestar Social</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>76.005.909-9</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>46674180</v>
+        <v>45955.02</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>4090-386-CM25</t>
+          <t>2129-337-CM25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5259,22 +5259,22 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>69.220.500-6</t>
+          <t>69.150.300-3</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAULLIN</t>
+          <t>Ilustre Municipalidad de Ranquil</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5290,133 +5290,11 @@
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>37160999.89</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>2974-641-CM25</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>2239-8-LR23</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>nov-2025</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>61.103.006-1</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Division de Bienestar Social</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>Maritano y Ebensperger Ltda.</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>86.519.000-K</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="n">
-        <v>43000000.26</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>2129-337-CM25</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>2239-8-LR23</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>nov-2025</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>69.150.300-3</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Ilustre Municipalidad de Ranquil</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>76.296.863-0</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="n">
-        <v>28490000.63</v>
+        <v>30447.88</v>
       </c>
     </row>
   </sheetData>
